--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones_Video_583_EXP6_CTRL4_40V.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones_Video_583_EXP6_CTRL4_40V.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -794,312 +782,312 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1347,52 +1335,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1447,87 +1435,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1607,32 +1595,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1773,27 +1761,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -1916,117 +1904,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2485,112 +2473,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>

--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones_Video_583_EXP6_CTRL4_40V.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones_Video_583_EXP6_CTRL4_40V.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="trenes_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="grilla_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="eventos_Video_583_EXP6_CTR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cinetica_Video_583_EXP6_CTR" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cin_grupos_Video_583_EXP6_C" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trenes_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_583_EXP6_CTR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_583_EXP6_CTRL4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_583_EXP6_CTR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_583_EXP6_C" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -778,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,162 +935,227 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1213,111 +1279,158 @@
           <t>1.283-1.322</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>6</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1.258-1.329</t>
+        </is>
       </c>
       <c r="AF2" t="n">
-        <v>6</v>
+        <v>3.095449999999971</v>
       </c>
       <c r="AG2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.189023278595867</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.1662-0.1906</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.157-0.1921</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR2" t="n">
         <v>8</v>
       </c>
-      <c r="AH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.2578112034419462</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.2541-0.2808</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.1291666666666709</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.3350000000000009</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.1810278981632827</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.1589-0.1844</t>
-        </is>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2524442389397539</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.25-0.2745</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.2476-0.2819</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
         <v>0.09916666666666529</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AX2" t="n">
         <v>0.3008333333333342</v>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
       </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>2</v>
       </c>
-      <c r="BB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="n">
         <v>0.5999999999999659</v>
       </c>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
         </is>
       </c>
-      <c r="BF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>6 ev en k=12.532-24.421</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>0.1061541600000265</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BM2" t="n">
         <v>0.07820715000000472</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BN2" t="n">
         <v>1.357345971564238</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.1893499999999846</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.08008370468335657</v>
+      </c>
+      <c r="BS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.08 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1757,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +1899,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1802,6 +1925,12 @@
       </c>
       <c r="E2" t="b">
         <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1820,6 +1949,12 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1837,6 +1972,12 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1854,6 +1995,12 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1871,6 +2018,12 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1887,6 +2040,12 @@
       </c>
       <c r="E7" t="b">
         <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1900,562 +2059,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tren</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>320</v>
-      </c>
-      <c r="E2" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.072699999999941</v>
-      </c>
-      <c r="G2" t="n">
-        <v>236.4120570482091</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.29972220468153</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10.99516567312469</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2248343268753139</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1300000000000008</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3683333333333394</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.2227906568317479</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.0666666666666611</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2999999999999989</v>
-      </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>11.57682268563163</v>
-      </c>
-      <c r="V2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5816570125069465</v>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>622</v>
-      </c>
-      <c r="E3" t="n">
-        <v>21.28666666666667</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.15440000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>236.3805482885453</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.334458365055272</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20.99902982187475</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2876368447919226</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.128333333333341</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.370000000000001</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.1515656249999928</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.06333333333333968</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2999999999999901</v>
-      </c>
-      <c r="T3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>21.5769019607843</v>
-      </c>
-      <c r="V3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.5778721389095587</v>
+          <t>0-10 s</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>922</v>
-      </c>
-      <c r="E4" t="n">
-        <v>31.28833333333333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.127700000000004</v>
-      </c>
-      <c r="G4" t="n">
-        <v>236.3647913522242</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.323251226253572</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30.99729975162994</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2910335817033953</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1316666666666713</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.3316666666666599</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.1453174834694764</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3016666666666694</v>
-      </c>
-      <c r="T4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>31.59239592378196</v>
-      </c>
-      <c r="V4" t="n">
-        <v>19</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.5950961721520294</v>
+          <t>0.1893499999999846</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1221</v>
-      </c>
-      <c r="E5" t="n">
-        <v>41.25333333333334</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.118200000000002</v>
-      </c>
-      <c r="G5" t="n">
-        <v>236.3478914650513</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.319326345867185</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>40.99959028760019</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2537430457331453</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.1300000000000097</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3299999999999983</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1854311543810852</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.2999999999999901</v>
-      </c>
-      <c r="T5" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>41.57972653205808</v>
-      </c>
-      <c r="V5" t="n">
-        <v>18</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.5801362444578899</v>
+          <t>0.08008370468335657</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1521</v>
-      </c>
-      <c r="E6" t="n">
-        <v>51.25666666666667</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.925799999999981</v>
-      </c>
-      <c r="G6" t="n">
-        <v>236.2883785333897</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.238232712992501</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>50.99636048830894</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.2603061783577232</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.336666666666666</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.1808406407108691</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="T6" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>51.55164392764858</v>
-      </c>
-      <c r="V6" t="n">
-        <v>17</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.5552834393396324</v>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_n_contracciones</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>estimulados</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1813</v>
-      </c>
-      <c r="E7" t="n">
-        <v>61.25333333333334</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.019999999999982</v>
-      </c>
-      <c r="G7" t="n">
-        <v>236.3086006907343</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.277989878985558</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>60.99801710480717</v>
-      </c>
-      <c r="K7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2553162285261692</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="O7" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.1812151556156962</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3350000000000009</v>
-      </c>
-      <c r="T7" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>61.60161535994869</v>
-      </c>
-      <c r="V7" t="n">
-        <v>19</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.6035982551415202</v>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>basal_instantes_s</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>basal_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0 contraccion(es) en 10.0 s; actividad basal 0.08 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2469,15 +2189,653 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>frame_llega_max</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>320</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.072699999999941</v>
+      </c>
+      <c r="G2" t="n">
+        <v>236.4120570482091</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.29972220468153</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>319</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11.18833333333333</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10.99516567312469</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1931676602086441</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1300000000000008</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3683333333333394</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2544573234984178</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0666666666666611</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2999999999999989</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>11.57682268563163</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5816570125069465</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>622</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.28666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.15440000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>236.3805482885453</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.334458365055272</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>619</v>
+      </c>
+      <c r="K3" t="n">
+        <v>21.18833333333334</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20.99902982187475</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1893035114585935</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.128333333333341</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.370000000000001</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.249898958333322</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.06333333333333968</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21.5769019607843</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5778721389095587</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>922</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.28833333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.127700000000004</v>
+      </c>
+      <c r="G4" t="n">
+        <v>236.3647913522242</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.323251226253572</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>919</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31.18833333333334</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30.99729975162994</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1910335817034046</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1316666666666713</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3316666666666599</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2453174834694671</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3016666666666694</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>31.59239592378196</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5950961721520294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41.25333333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.118200000000002</v>
+      </c>
+      <c r="G5" t="n">
+        <v>236.3478914650513</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.319326345867185</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1219</v>
+      </c>
+      <c r="K5" t="n">
+        <v>41.18833333333333</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40.99959028760019</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1887430457331405</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1300000000000097</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3299999999999983</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.25043115438109</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>41.57972653205808</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5801362444578899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E6" t="n">
+        <v>51.25666666666667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.925799999999981</v>
+      </c>
+      <c r="G6" t="n">
+        <v>236.2883785333897</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.238232712992501</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1518</v>
+      </c>
+      <c r="K6" t="n">
+        <v>51.155</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50.99636048830894</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1586395116910566</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.336666666666666</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2825073073775357</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>51.55164392764858</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5552834393396324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1813</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61.25333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.019999999999982</v>
+      </c>
+      <c r="G7" t="n">
+        <v>236.3086006907343</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.277989878985558</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1810</v>
+      </c>
+      <c r="K7" t="n">
+        <v>61.15333333333334</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>60.99801710480717</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1553162285261749</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2812151556156905</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>61.60161535994869</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.6035982551415202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
@@ -2500,85 +2858,105 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -2604,59 +2982,77 @@
           <t>1.283-1.322</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.258-1.329</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3.095449999999971</v>
       </c>
       <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.189023278595867</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.1662-0.1906</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.157-0.1921</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
         <v>8</v>
       </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.2578112034419462</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.2541-0.2808</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1291666666666709</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3350000000000009</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1810278981632827</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.1589-0.1844</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2524442389397539</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.25-0.2745</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.2476-0.2819</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
         <v>0.09916666666666529</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>0.3008333333333342</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
@@ -2682,59 +3078,77 @@
           <t>1.283-1.322</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>6</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.258-1.329</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>3.095449999999971</v>
       </c>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.189023278595867</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.1662-0.1906</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.157-0.1921</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.2578112034419462</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.2541-0.2808</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.1291666666666709</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3350000000000009</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1810278981632827</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.1589-0.1844</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2524442389397539</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.25-0.2745</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2476-0.2819</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>0.09916666666666529</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
         <v>0.3008333333333342</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
